--- a/Employee_Reports_wi52/Mabin Pauly Q0583.xlsx
+++ b/Employee_Reports_wi52/Mabin Pauly Q0583.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -860,11 +860,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -909,11 +909,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-252</v>
+        <v>-260</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-163</v>
+        <v>-171</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -1056,11 +1056,11 @@
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-160</v>
+        <v>-168</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1105,11 +1105,11 @@
         </is>
       </c>
       <c r="H14" s="5" t="n">
-        <v>-148</v>
+        <v>-156</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1154,11 +1154,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1182,20 +1182,20 @@
       <c r="E16" s="3" t="inlineStr"/>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>05-Jul-2025</t>
+          <t>24-Aug-2026</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>05-Jul-2027</t>
+          <t>23-Aug-2028</t>
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>319</v>
+        <v>726</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7601</v>
+        <v>7593</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7800</v>
+        <v>7792</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
